--- a/src/app/resources/inventory/ComponentInventory.xlsx
+++ b/src/app/resources/inventory/ComponentInventory.xlsx
@@ -719,136 +719,32 @@
           <t>FZ</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>ZA</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>ZB</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>ZC</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>ZD</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>ZE</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>ZF</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>ZG</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>ZH</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>ZI</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>ZJ</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>ZK</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>ZL</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>ZN</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>ZO</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>ZP</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>ZQ</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>ZR</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>ZS</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>ZT</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>ZU</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>ZV</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>ZW</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>ZX</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>ZY</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>ZZ</t>
-        </is>
-      </c>
+      <c r="BE1" s="1" t="n"/>
+      <c r="BF1" s="1" t="n"/>
+      <c r="BG1" s="1" t="n"/>
+      <c r="BH1" s="1" t="n"/>
+      <c r="BI1" s="1" t="n"/>
+      <c r="BJ1" s="1" t="n"/>
+      <c r="BK1" s="1" t="n"/>
+      <c r="BL1" s="1" t="n"/>
+      <c r="BM1" s="1" t="n"/>
+      <c r="BN1" s="1" t="n"/>
+      <c r="BO1" s="1" t="n"/>
+      <c r="BP1" s="1" t="n"/>
+      <c r="BQ1" s="1" t="n"/>
+      <c r="BR1" s="1" t="n"/>
+      <c r="BS1" s="1" t="n"/>
+      <c r="BT1" s="1" t="n"/>
+      <c r="BU1" s="1" t="n"/>
+      <c r="BV1" s="1" t="n"/>
+      <c r="BW1" s="1" t="n"/>
+      <c r="BX1" s="1" t="n"/>
+      <c r="BY1" s="1" t="n"/>
+      <c r="BZ1" s="1" t="n"/>
+      <c r="CA1" s="1" t="n"/>
+      <c r="CB1" s="1" t="n"/>
+      <c r="CC1" s="1" t="n"/>
+      <c r="CD1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1054,16 +950,18 @@
           <t>围护|横列板|m2</t>
         </is>
       </c>
-      <c r="BE6" s="0" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
+      <c r="BE6" s="0" t="n"/>
+      <c r="BF6" s="0" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -1093,16 +991,18 @@
           <t>1*sides*height</t>
         </is>
       </c>
-      <c r="BE7" s="0" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>ROUND(count/B,0)/count*A*width*C/1000</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>1*sides*2*A*D/1000</t>
         </is>
       </c>
+      <c r="BE7" s="0" t="n"/>
+      <c r="BF7" s="0" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -1165,16 +1065,18 @@
           <t>围护|B|t</t>
         </is>
       </c>
-      <c r="BE8" s="0" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
+      <c r="BE8" s="0" t="n"/>
+      <c r="BF8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -1221,16 +1123,18 @@
           <t>ROUND(count/(C/1000),0)/count*D*E/1000*sides</t>
         </is>
       </c>
-      <c r="BE9" s="0" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>ROUND(count/G,0)/count*F*width*H/1000</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>1*sides*2*F*I/1000</t>
         </is>
       </c>
+      <c r="BE9" s="0" t="n"/>
+      <c r="BF9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -1328,46 +1232,54 @@
           <t>围护|φ A 灌注桩钢筋|t</t>
         </is>
       </c>
-      <c r="BE10" s="0" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>支撑|砼围檩砼|m3</t>
         </is>
       </c>
-      <c r="BF10" s="0" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>支撑|砼围檩模板|m2</t>
         </is>
       </c>
-      <c r="BG10" s="0" t="inlineStr">
+      <c r="AI10" t="inlineStr">
         <is>
           <t>支撑|砼围檩钢筋|t</t>
         </is>
       </c>
-      <c r="BH10" s="0" t="inlineStr">
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>支撑|砼围檩砼|m3</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>支撑|砼围檩模板|m2</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>支撑|砼围檩钢筋|t</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
+      <c r="BE10" s="0" t="n"/>
+      <c r="BF10" s="0" t="n"/>
+      <c r="BG10" s="0" t="n"/>
+      <c r="BH10" s="0" t="n"/>
+      <c r="BI10" s="0" t="n"/>
+      <c r="BJ10" s="0" t="n"/>
+      <c r="BK10" s="0" t="n"/>
+      <c r="BL10" s="0" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
@@ -1437,49 +1349,54 @@
           <t>PI()*(A/1000*A/1000)/4*C*ROUND(count/B,2)/count*D/1000*sides</t>
         </is>
       </c>
-      <c r="AG11" s="2" t="n"/>
-      <c r="AH11" s="2" t="n"/>
-      <c r="AI11" s="2" t="n"/>
-      <c r="BE11" s="2" t="inlineStr">
+      <c r="AG11" s="2" t="inlineStr">
         <is>
           <t>1*E/1000*F/1000*sides</t>
         </is>
       </c>
-      <c r="BF11" s="2" t="inlineStr">
+      <c r="AH11" s="2" t="inlineStr">
         <is>
           <t>1*F/1000*sides</t>
         </is>
       </c>
-      <c r="BG11" s="2" t="inlineStr">
+      <c r="AI11" s="2" t="inlineStr">
         <is>
           <t>1*E/1000*F/1000*G/1000</t>
         </is>
       </c>
-      <c r="BH11" s="0" t="inlineStr">
+      <c r="AJ11" t="inlineStr">
         <is>
           <t>ROUND(count/L,0)/count*K*width*M/1000</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>ROUND(count/L)/count*H/1000*I/1000*width</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>ROUND(count/L)/count*I/1000*2*width</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>ROUND(count/L)/count*H/1000*I/1000*width*J/1000</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>1*sides*2*K*N/1000</t>
         </is>
       </c>
+      <c r="BE11" s="2" t="n"/>
+      <c r="BF11" s="2" t="n"/>
+      <c r="BG11" s="2" t="n"/>
+      <c r="BH11" s="0" t="n"/>
+      <c r="BI11" s="0" t="n"/>
+      <c r="BJ11" s="0" t="n"/>
+      <c r="BK11" s="0" t="n"/>
+      <c r="BL11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -1567,16 +1484,18 @@
           <t>围护|插拔型钢|t</t>
         </is>
       </c>
-      <c r="BE12" s="0" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>支撑|钢支撑、钢围檩|t</t>
         </is>
       </c>
+      <c r="BE12" s="0" t="n"/>
+      <c r="BF12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -1642,19 +1561,19 @@
           <t>ROUND(count/(F/1000),0)/count*G*H/1000*sides</t>
         </is>
       </c>
-      <c r="AG13" s="2" t="n"/>
-      <c r="AH13" s="2" t="n"/>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>ROUND(count/J,0)/count*I*width*K/1000</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>1*sides*2*I*L/1000</t>
+        </is>
+      </c>
       <c r="AI13" s="2" t="n"/>
-      <c r="BE13" s="0" t="inlineStr">
-        <is>
-          <t>ROUND(count/J,0)/count*I*width*K/1000</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>1*sides*2*I*L/1000</t>
-        </is>
-      </c>
+      <c r="BE13" s="0" t="n"/>
+      <c r="BF13" s="0" t="n"/>
       <c r="BG13" s="2" t="n"/>
     </row>
   </sheetData>
